--- a/data/fmsForecastOutput/File1/RPT_RPT3432412844991PL_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT3432412844991PL_fmsForecastOutput.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>453.7323818790083</v>
+        <v>453.7323818790082</v>
       </c>
       <c r="D8" s="149" t="n">
         <v>477.8161195224901</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>508.5117584209895</v>
+        <v>508.5117584209896</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>536.7661157221922</v>
+        <v>536.7661157221921</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>564.1004634540957</v>
+        <v>564.1004634540958</v>
       </c>
       <c r="H8" s="148" t="n">
         <v>449.4964055209358</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>474.5635455336747</v>
+        <v>474.5635455336746</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>506.178821356474</v>
+        <v>506.1788213564741</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>535.4044950830053</v>
+        <v>535.4044950830051</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>563.8599622534322</v>
+        <v>563.8599622534323</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>48443317.48582028</v>
+        <v>48443317.48582027</v>
       </c>
       <c r="N8" s="152" t="n">
         <v>56057872.88373958</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>64687612.43947388</v>
+        <v>64687612.4394739</v>
       </c>
       <c r="P8" s="152" t="n">
         <v>73688221.4552092</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>85739817.18971768</v>
+        <v>85739817.18971771</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,19 +1925,19 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>469.3311561503295</v>
+        <v>469.3311561503294</v>
       </c>
       <c r="U8" s="149" t="n">
         <v>494.2428637649088</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>525.99378185752</v>
+        <v>525.9937818575202</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>555.2194900239565</v>
+        <v>555.2194900239564</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>583.4935597972051</v>
+        <v>583.4935597972052</v>
       </c>
       <c r="Y8" s="148" t="n">
         <v>465.6736692480497</v>
@@ -1946,28 +1946,28 @@
         <v>491.4356642878187</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>523.9810384304666</v>
+        <v>523.9810384304667</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>554.0451521575277</v>
+        <v>554.0451521575275</v>
       </c>
       <c r="AC8" s="150" t="n">
         <v>583.2862110127645</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>48443317.48582028</v>
+        <v>48443317.48582027</v>
       </c>
       <c r="AE8" s="152" t="n">
         <v>56057872.88373958</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>64687612.43947388</v>
+        <v>64687612.4394739</v>
       </c>
       <c r="AG8" s="152" t="n">
         <v>73688221.4552092</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>85739817.18971768</v>
+        <v>85739817.18971771</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>886.9065937671726</v>
+        <v>886.9065937671725</v>
       </c>
       <c r="D9" s="156" t="n">
         <v>922.5011236668605</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>970.5771370632123</v>
+        <v>970.5771370632121</v>
       </c>
       <c r="F9" s="156" t="n">
         <v>1009.617760662079</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>1048.414368770601</v>
+        <v>1048.4143687706</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>877.7666989440918</v>
+        <v>877.7666989440916</v>
       </c>
       <c r="I9" s="156" t="n">
         <v>915.1597728184979</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>965.011786132048</v>
+        <v>965.0117861320479</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>1005.981766253667</v>
+        <v>1005.981766253666</v>
       </c>
       <c r="L9" s="157" t="n">
         <v>1046.953055157396</v>
@@ -2055,13 +2055,13 @@
         <v>20284595.06762622</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>22558342.41644684</v>
+        <v>22558342.41644685</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>25407144.36613054</v>
+        <v>25407144.36613053</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>28372025.05451233</v>
+        <v>28372025.05451232</v>
       </c>
       <c r="Q9" s="160" t="n">
         <v>32431022.39418732</v>
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>897.7850354383371</v>
+        <v>897.785035438337</v>
       </c>
       <c r="U9" s="156" t="n">
         <v>933.8161536101693</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>982.4818481648188</v>
+        <v>982.4818481648185</v>
       </c>
       <c r="W9" s="156" t="n">
         <v>1022.001328443307</v>
@@ -2087,13 +2087,13 @@
         <v>1061.27380023501</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>888.4525922009534</v>
+        <v>888.4525922009532</v>
       </c>
       <c r="Z9" s="156" t="n">
         <v>926.319989350736</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>976.7990248328261</v>
+        <v>976.7990248328259</v>
       </c>
       <c r="AB9" s="156" t="n">
         <v>1018.28851656949</v>
@@ -2105,13 +2105,13 @@
         <v>20284595.06762622</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>22558342.41644684</v>
+        <v>22558342.41644685</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>25407144.36613054</v>
+        <v>25407144.36613053</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>28372025.05451233</v>
+        <v>28372025.05451232</v>
       </c>
       <c r="AH9" s="160" t="n">
         <v>32431022.39418732</v>
@@ -2173,31 +2173,31 @@
         <v>530.1547633621515</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>554.5160055734442</v>
+        <v>554.5160055734441</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>587.3688218566052</v>
+        <v>587.3688218566051</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>617.1124255378742</v>
+        <v>617.1124255378741</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>645.9989994181688</v>
+        <v>645.9989994181689</v>
       </c>
       <c r="H10" s="161" t="n">
         <v>525.1145653025592</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>550.6311380611705</v>
+        <v>550.6311380611704</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>584.5590906515858</v>
+        <v>584.5590906515857</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>615.4352528808711</v>
+        <v>615.4352528808708</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>645.617807975568</v>
+        <v>645.6178079755681</v>
       </c>
       <c r="M10" s="164" t="n">
         <v>68727912.55344649</v>
@@ -2229,7 +2229,7 @@
         <v>605.3051833089822</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>635.9673521794617</v>
+        <v>635.9673521794616</v>
       </c>
       <c r="X10" s="163" t="n">
         <v>665.748341463674</v>
@@ -2241,10 +2241,10 @@
         <v>567.9449225898655</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>602.7827405677925</v>
+        <v>602.7827405677924</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>634.4550348748437</v>
+        <v>634.4550348748436</v>
       </c>
       <c r="AC10" s="163" t="n">
         <v>665.3912311256923</v>
@@ -2318,43 +2318,43 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>850.0609933811985</v>
+        <v>850.0609933811986</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>881.131792044073</v>
+        <v>881.1317920440731</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>916.5874711014275</v>
+        <v>916.5874711014276</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>944.7441463407799</v>
+        <v>944.7441463407796</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>966.2765364458013</v>
+        <v>966.2765364458008</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>846.0540161561986</v>
+        <v>846.0540161561987</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>878.652144285428</v>
+        <v>878.6521442854281</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>915.6560392100143</v>
+        <v>915.6560392100145</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>944.7441463407799</v>
+        <v>944.7441463407796</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>966.2765364458013</v>
+        <v>966.2765364458008</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>6878510.999352514</v>
+        <v>6878510.999352515</v>
       </c>
       <c r="N11" s="159" t="n">
         <v>7791328.033578638</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>8868139.370904427</v>
+        <v>8868139.370904429</v>
       </c>
       <c r="P11" s="159" t="n">
         <v>10057877.14096342</v>
@@ -2398,13 +2398,13 @@
         <v>1185.135770170734</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>6878510.999352514</v>
+        <v>6878510.999352515</v>
       </c>
       <c r="AE11" s="159" t="n">
         <v>7791328.033578638</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>8868139.370904427</v>
+        <v>8868139.370904429</v>
       </c>
       <c r="AG11" s="159" t="n">
         <v>10057877.14096342</v>
@@ -2470,22 +2470,22 @@
         <v>606.9027567388092</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>636.9273366028626</v>
+        <v>636.9273366028624</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>665.8055489039085</v>
+        <v>665.8055489039086</v>
       </c>
       <c r="H12" s="161" t="n">
         <v>543.8847092956677</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>569.8123650292849</v>
+        <v>569.8123650292848</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>604.1347661022556</v>
+        <v>604.1347661022555</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>635.3007351654452</v>
+        <v>635.3007351654451</v>
       </c>
       <c r="L12" s="163" t="n">
         <v>665.4369529019585</v>
@@ -2497,7 +2497,7 @@
         <v>86407543.33376507</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>98962896.17650884</v>
+        <v>98962896.17650886</v>
       </c>
       <c r="P12" s="165" t="n">
         <v>112118123.6506849</v>
@@ -2514,16 +2514,16 @@
         <v>571.0054171648112</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>596.7851914068322</v>
+        <v>596.785191406832</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>631.4214883221683</v>
+        <v>631.4214883221684</v>
       </c>
       <c r="W12" s="162" t="n">
         <v>662.7916373686359</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>693.0065319647402</v>
+        <v>693.0065319647404</v>
       </c>
       <c r="Y12" s="161" t="n">
         <v>566.3778224292082</v>
@@ -2532,7 +2532,7 @@
         <v>593.2393612941519</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>628.8874034482828</v>
+        <v>628.887403448283</v>
       </c>
       <c r="AB12" s="162" t="n">
         <v>661.296224521666</v>
@@ -2547,7 +2547,7 @@
         <v>86407543.33376507</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>98962896.17650884</v>
+        <v>98962896.17650886</v>
       </c>
       <c r="AG12" s="165" t="n">
         <v>112118123.6506849</v>
@@ -2606,43 +2606,43 @@
         <v>4766.792673747266</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>4848.432407797191</v>
+        <v>4848.43240779719</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>5381.071504192175</v>
+        <v>5381.071504192173</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>5589.15867494974</v>
+        <v>5589.158674949739</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>5946.923358162598</v>
+        <v>5946.923358162595</v>
       </c>
       <c r="H13" s="155" t="n">
         <v>4759.461506208725</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>4841.238526563639</v>
+        <v>4841.238526563638</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>5373.244843865687</v>
+        <v>5373.244843865686</v>
       </c>
       <c r="K13" s="156" t="n">
         <v>5581.820641199548</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>5939.801099897693</v>
+        <v>5939.801099897692</v>
       </c>
       <c r="M13" s="158" t="n">
         <v>6695828.650701695</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>7243139.520317764</v>
+        <v>7243139.520317763</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>8450119.12970455</v>
+        <v>8450119.129704546</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>9921924.315029263</v>
+        <v>9921924.315029262</v>
       </c>
       <c r="Q13" s="160" t="n">
         <v>11809165.1540955</v>
@@ -2659,40 +2659,40 @@
         <v>3947.288922595854</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>4380.930196332124</v>
+        <v>4380.930196332122</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>4550.341691632073</v>
+        <v>4550.341691632072</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>4841.611209728488</v>
+        <v>4841.611209728485</v>
       </c>
       <c r="Y13" s="155" t="n">
         <v>3875.039677291378</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>3941.613927359101</v>
+        <v>3941.6139273591</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>4374.756029952748</v>
+        <v>4374.756029952746</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>4544.553010384676</v>
+        <v>4544.553010384675</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>4835.992765262454</v>
+        <v>4835.992765262452</v>
       </c>
       <c r="AD13" s="158" t="n">
         <v>6695828.650701695</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>7243139.520317764</v>
+        <v>7243139.520317763</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>8450119.12970455</v>
+        <v>8450119.129704546</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>9921924.315029263</v>
+        <v>9921924.315029262</v>
       </c>
       <c r="AH13" s="160" t="n">
         <v>11809165.1540955</v>
@@ -2752,28 +2752,28 @@
         <v>615.674129235693</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>652.4409884787702</v>
+        <v>652.4409884787704</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>686.3705472427977</v>
+        <v>686.3705472427974</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>719.0469839119924</v>
+        <v>719.0469839119922</v>
       </c>
       <c r="H14" s="167" t="n">
         <v>586.1202988364053</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>611.543446684561</v>
+        <v>611.5434466845609</v>
       </c>
       <c r="J14" s="168" t="n">
         <v>649.4845771713776</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>684.6261697101233</v>
+        <v>684.6261697101232</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>718.6442413931477</v>
+        <v>718.6442413931476</v>
       </c>
       <c r="M14" s="170" t="n">
         <v>82302252.20350072</v>
@@ -2799,31 +2799,31 @@
         <v>613.5793287970733</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>638.7161705625663</v>
+        <v>638.7161705625662</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>677.0047809187236</v>
+        <v>677.0047809187237</v>
       </c>
       <c r="W14" s="168" t="n">
         <v>712.2644734439658</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>746.3278344159346</v>
+        <v>746.3278344159345</v>
       </c>
       <c r="Y14" s="167" t="n">
         <v>608.6585622728392</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>634.9570462496329</v>
+        <v>634.9570462496328</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>674.309133185536</v>
+        <v>674.3091331855361</v>
       </c>
       <c r="AB14" s="168" t="n">
         <v>710.6663496950868</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>745.9422402406755</v>
+        <v>745.9422402406753</v>
       </c>
       <c r="AD14" s="170" t="n">
         <v>82302252.20350072</v>
@@ -3185,13 +3185,13 @@
         <v>107772.4246307993</v>
       </c>
       <c r="N19" s="75" t="n">
-        <v>118125.1139311579</v>
+        <v>118125.113931158</v>
       </c>
       <c r="O19" s="75" t="n">
         <v>127795.9679666604</v>
       </c>
       <c r="P19" s="75" t="n">
-        <v>137630.9353618428</v>
+        <v>137630.9353618429</v>
       </c>
       <c r="Q19" s="76" t="n">
         <v>152058.7077100912</v>
@@ -3211,7 +3211,7 @@
         <v>122981.7056221328</v>
       </c>
       <c r="W19" s="75" t="n">
-        <v>132719.082775768</v>
+        <v>132719.0827757681</v>
       </c>
       <c r="X19" s="76" t="n">
         <v>146942.1825658484</v>
@@ -3238,7 +3238,7 @@
         <v>114069.6065780611</v>
       </c>
       <c r="AF19" s="75" t="n">
-        <v>123454.1093953308</v>
+        <v>123454.1093953309</v>
       </c>
       <c r="AG19" s="75" t="n">
         <v>133000.3902538578</v>
@@ -3298,10 +3298,10 @@
         <v>26177.35715783279</v>
       </c>
       <c r="F20" s="80" t="n">
-        <v>28101.74915693515</v>
+        <v>28101.74915693516</v>
       </c>
       <c r="G20" s="81" t="n">
-        <v>30933.40129649007</v>
+        <v>30933.40129649008</v>
       </c>
       <c r="H20" s="79" t="n">
         <v>238.1499839334398</v>
@@ -3322,7 +3322,7 @@
         <v>23109.32402884223</v>
       </c>
       <c r="N20" s="80" t="n">
-        <v>24649.62194193909</v>
+        <v>24649.6219419391</v>
       </c>
       <c r="O20" s="80" t="n">
         <v>26328.32544767897</v>
@@ -3331,7 +3331,7 @@
         <v>28203.3193903418</v>
       </c>
       <c r="Q20" s="81" t="n">
-        <v>30976.57744483274</v>
+        <v>30976.57744483275</v>
       </c>
       <c r="S20" s="32" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>22594.04452840141</v>
       </c>
       <c r="U20" s="80" t="n">
-        <v>24157.15591258024</v>
+        <v>24157.15591258025</v>
       </c>
       <c r="V20" s="80" t="n">
         <v>25860.16669273701</v>
@@ -3369,7 +3369,7 @@
         <v>43.0277284640058</v>
       </c>
       <c r="AD20" s="79" t="n">
-        <v>22831.37586145753</v>
+        <v>22831.37586145754</v>
       </c>
       <c r="AE20" s="80" t="n">
         <v>24352.64560387835</v>
@@ -3381,7 +3381,7 @@
         <v>27862.46195733875</v>
       </c>
       <c r="AH20" s="81" t="n">
-        <v>30601.60967687896</v>
+        <v>30601.60967687897</v>
       </c>
       <c r="AS20" s="82" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>153387.0260951633</v>
       </c>
       <c r="F21" s="86" t="n">
-        <v>165383.5545780268</v>
+        <v>165383.5545780269</v>
       </c>
       <c r="G21" s="87" t="n">
         <v>182927.279593835</v>
@@ -3442,13 +3442,13 @@
         <v>130881.7486596416</v>
       </c>
       <c r="N21" s="86" t="n">
-        <v>142774.735873097</v>
+        <v>142774.7358730971</v>
       </c>
       <c r="O21" s="86" t="n">
         <v>154124.2934143394</v>
       </c>
       <c r="P21" s="86" t="n">
-        <v>165834.2547521846</v>
+        <v>165834.2547521847</v>
       </c>
       <c r="Q21" s="87" t="n">
         <v>183035.2851549239</v>
@@ -3468,10 +3468,10 @@
         <v>148841.8723148698</v>
       </c>
       <c r="W21" s="86" t="n">
-        <v>160480.3236517736</v>
+        <v>160480.3236517737</v>
       </c>
       <c r="X21" s="87" t="n">
-        <v>177500.7645142633</v>
+        <v>177500.7645142634</v>
       </c>
       <c r="Y21" s="85" t="n">
         <v>1048.022775568631</v>
@@ -3498,10 +3498,10 @@
         <v>149464.7254178835</v>
       </c>
       <c r="AG21" s="86" t="n">
-        <v>160862.8522111965</v>
+        <v>160862.8522111966</v>
       </c>
       <c r="AH21" s="87" t="n">
-        <v>177596.0278045541</v>
+        <v>177596.0278045542</v>
       </c>
       <c r="AR21" s="20" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>8680.114303973094</v>
       </c>
       <c r="X22" s="81" t="n">
-        <v>9831.461489368954</v>
+        <v>9831.461489368956</v>
       </c>
       <c r="Y22" s="79" t="n">
         <v>33.82845994569738</v>
@@ -3658,7 +3658,7 @@
         <v>8680.114303973094</v>
       </c>
       <c r="AH22" s="81" t="n">
-        <v>9831.461489368954</v>
+        <v>9831.461489368956</v>
       </c>
       <c r="AR22" s="88" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>163062.1958421902</v>
       </c>
       <c r="F23" s="86" t="n">
-        <v>176029.69319653</v>
+        <v>176029.6931965301</v>
       </c>
       <c r="G23" s="87" t="n">
         <v>194985.542673434</v>
@@ -3736,7 +3736,7 @@
         <v>139011.8572200891</v>
       </c>
       <c r="N23" s="86" t="n">
-        <v>151642.0994643109</v>
+        <v>151642.099464311</v>
       </c>
       <c r="O23" s="86" t="n">
         <v>163809.305024764</v>
@@ -3951,7 +3951,7 @@
         <v>164632.5371995057</v>
       </c>
       <c r="F25" s="92" t="n">
-        <v>177804.9021129451</v>
+        <v>177804.9021129452</v>
       </c>
       <c r="G25" s="93" t="n">
         <v>196971.3031150725</v>
@@ -3981,10 +3981,10 @@
         <v>165381.9337389295</v>
       </c>
       <c r="P25" s="92" t="n">
-        <v>178257.9360315528</v>
+        <v>178257.9360315529</v>
       </c>
       <c r="Q25" s="93" t="n">
-        <v>197081.6897489414</v>
+        <v>197081.6897489415</v>
       </c>
       <c r="S25" s="51" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>134134.6560107474</v>
       </c>
       <c r="U25" s="92" t="n">
-        <v>146623.3159113499</v>
+        <v>146623.31591135</v>
       </c>
       <c r="V25" s="92" t="n">
         <v>158659.1680496694</v>
@@ -4004,7 +4004,7 @@
         <v>171340.916914783</v>
       </c>
       <c r="X25" s="93" t="n">
-        <v>189771.324196888</v>
+        <v>189771.3241968881</v>
       </c>
       <c r="Y25" s="91" t="n">
         <v>1084.42625463546</v>
@@ -4025,7 +4025,7 @@
         <v>135219.0822653829</v>
       </c>
       <c r="AE25" s="92" t="n">
-        <v>147491.367183386</v>
+        <v>147491.3671833861</v>
       </c>
       <c r="AF25" s="92" t="n">
         <v>159293.4308909304</v>
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>466.5108185975144</v>
+        <v>466.5108185975143</v>
       </c>
       <c r="D35" s="149" t="n">
         <v>502.8297901391587</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>538.5492284241141</v>
+        <v>538.5492284241142</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>575.6858242196328</v>
+        <v>575.6858242196327</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>606.52435876455</v>
+        <v>606.5243587645501</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>462.1555447019628</v>
+        <v>462.1555447019627</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>499.4069439240864</v>
+        <v>499.4069439240863</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>536.0784862332979</v>
+        <v>536.078486233298</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>574.2254755184294</v>
+        <v>574.2254755184293</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>606.265770364141</v>
+        <v>606.2657703641411</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>49807623.6090983</v>
+        <v>49807623.60909829</v>
       </c>
       <c r="N35" s="152" t="n">
         <v>58992502.14904411</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>68508669.05428635</v>
+        <v>68508669.05428636</v>
       </c>
       <c r="P35" s="152" t="n">
         <v>79031189.30420043</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>92187989.57043417</v>
+        <v>92187989.5704342</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,49 +4458,49 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>482.548900173919</v>
+        <v>482.5489001739189</v>
       </c>
       <c r="U35" s="149" t="n">
         <v>520.1164743312693</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>557.0639039987176</v>
+        <v>557.0639039987177</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>595.4772113496704</v>
+        <v>595.4772113496703</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>627.3759376693788</v>
+        <v>627.3759376693789</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>478.7884076965555</v>
+        <v>478.7884076965554</v>
       </c>
       <c r="Z35" s="149" t="n">
         <v>517.1623179805907</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>554.9322690823074</v>
+        <v>554.9322690823075</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>594.2177248754958</v>
+        <v>594.2177248754956</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>627.152994954967</v>
+        <v>627.1529949549671</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>49807623.6090983</v>
+        <v>49807623.60909829</v>
       </c>
       <c r="AE35" s="152" t="n">
         <v>58992502.14904411</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>68508669.05428635</v>
+        <v>68508669.05428636</v>
       </c>
       <c r="AG35" s="152" t="n">
         <v>79031189.30420043</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>92187989.57043417</v>
+        <v>92187989.5704342</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>912.2174117243515</v>
+        <v>912.2174117243513</v>
       </c>
       <c r="D36" s="156" t="n">
         <v>971.1499506686725</v>
@@ -4522,10 +4522,10 @@
         <v>1083.23093053413</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>1127.700007969134</v>
+        <v>1127.700007969133</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>902.8166797222029</v>
+        <v>902.8166797222027</v>
       </c>
       <c r="I36" s="156" t="n">
         <v>963.421447871961</v>
@@ -4534,7 +4534,7 @@
         <v>1022.399215977548</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>1079.329828790577</v>
+        <v>1079.329828790576</v>
       </c>
       <c r="L36" s="157" t="n">
         <v>1126.128183486044</v>
@@ -4543,10 +4543,10 @@
         <v>20863483.19034386</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>23747974.46079942</v>
+        <v>23747974.46079943</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>26918059.29570871</v>
+        <v>26918059.2957087</v>
       </c>
       <c r="P36" s="159" t="n">
         <v>30440683.88890356</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>923.406305768665</v>
+        <v>923.4063057686649</v>
       </c>
       <c r="U36" s="156" t="n">
         <v>983.0616876729379</v>
@@ -4575,16 +4575,16 @@
         <v>1141.531925383522</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>913.8075303453024</v>
+        <v>913.8075303453022</v>
       </c>
       <c r="Z36" s="156" t="n">
         <v>975.1702072573738</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>1034.887419520139</v>
+        <v>1034.887419520138</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>1092.533887906691</v>
+        <v>1092.53388790669</v>
       </c>
       <c r="AC36" s="157" t="n">
         <v>1139.926861916697</v>
@@ -4593,10 +4593,10 @@
         <v>20863483.19034386</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>23747974.46079942</v>
+        <v>23747974.46079943</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>26918059.29570871</v>
+        <v>26918059.2957087</v>
       </c>
       <c r="AG36" s="159" t="n">
         <v>30440683.88890356</v>
@@ -4615,13 +4615,13 @@
         <v>545.1442144800127</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>583.6063007325236</v>
+        <v>583.6063007325234</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>622.1303768598465</v>
+        <v>622.1303768598464</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>661.9271999106531</v>
+        <v>661.927199910653</v>
       </c>
       <c r="G37" s="163" t="n">
         <v>694.6562958851382</v>
@@ -4630,13 +4630,13 @@
         <v>539.9615112357843</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>579.5176303697458</v>
+        <v>579.5176303697457</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>619.1543606526392</v>
+        <v>619.1543606526391</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>660.1282307849722</v>
+        <v>660.1282307849718</v>
       </c>
       <c r="L37" s="163" t="n">
         <v>694.2463927184481</v>
@@ -4654,7 +4654,7 @@
         <v>109471873.193104</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>127071586.4589984</v>
+        <v>127071586.4589985</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4668,10 +4668,10 @@
         <v>601.4039546051119</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>641.1282448001133</v>
+        <v>641.1282448001132</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>682.1513734646192</v>
+        <v>682.151373464619</v>
       </c>
       <c r="X37" s="163" t="n">
         <v>715.8931783011413</v>
@@ -4683,10 +4683,10 @@
         <v>597.7397080715831</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>638.4565193104568</v>
+        <v>638.4565193104567</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>680.5292315057212</v>
+        <v>680.5292315057211</v>
       </c>
       <c r="AC37" s="163" t="n">
         <v>715.5091700521688</v>
@@ -4704,7 +4704,7 @@
         <v>109471873.193104</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>127071586.4589984</v>
+        <v>127071586.4589985</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4714,34 +4714,34 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>874.175903151487</v>
+        <v>874.1759031514871</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>927.4499101757548</v>
+        <v>927.4499101757549</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>970.9405499143443</v>
+        <v>970.9405499143444</v>
       </c>
       <c r="F38" s="156" t="n">
         <v>1013.467471736314</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>1039.189525104701</v>
+        <v>1039.1895251047</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>870.0552542076516</v>
+        <v>870.0552542076517</v>
       </c>
       <c r="I38" s="156" t="n">
-        <v>924.8399157211365</v>
+        <v>924.8399157211367</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>969.9538846790344</v>
+        <v>969.9538846790346</v>
       </c>
       <c r="K38" s="156" t="n">
         <v>1013.467471736314</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>1039.189525104701</v>
+        <v>1039.1895251047</v>
       </c>
       <c r="M38" s="158" t="n">
         <v>7073643.670295971</v>
@@ -4750,13 +4750,13 @@
         <v>8200891.79636695</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>9394014.63469293</v>
+        <v>9394014.634692932</v>
       </c>
       <c r="P38" s="159" t="n">
         <v>10789515.18944878</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>12530820.68327602</v>
+        <v>12530820.68327601</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4767,13 +4767,13 @@
         <v>1072.174572360886</v>
       </c>
       <c r="U38" s="156" t="n">
-        <v>1137.515009558108</v>
+        <v>1137.515009558109</v>
       </c>
       <c r="V38" s="156" t="n">
         <v>1190.856171097016</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1243.01533500661</v>
+        <v>1243.015335006609</v>
       </c>
       <c r="X38" s="157" t="n">
         <v>1274.563369528117</v>
@@ -4785,10 +4785,10 @@
         <v>1134.050106951171</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>1189.546127358325</v>
+        <v>1189.546127358326</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>1243.01533500661</v>
+        <v>1243.015335006609</v>
       </c>
       <c r="AC38" s="157" t="n">
         <v>1274.563369528117</v>
@@ -4800,13 +4800,13 @@
         <v>8200891.79636695</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>9394014.63469293</v>
+        <v>9394014.634692932</v>
       </c>
       <c r="AG38" s="159" t="n">
         <v>10789515.18944878</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>12530820.68327602</v>
+        <v>12530820.68327601</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4822,28 +4822,28 @@
         <v>603.7926562237801</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>642.8267597115663</v>
+        <v>642.8267597115664</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>683.1880815033051</v>
+        <v>683.1880815033048</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>715.9628618009059</v>
+        <v>715.962861800906</v>
       </c>
       <c r="H39" s="161" t="n">
         <v>559.2670440094154</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>599.7105601113996</v>
+        <v>599.7105601113994</v>
       </c>
       <c r="J39" s="162" t="n">
         <v>639.8949251926905</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>681.4433381840328</v>
+        <v>681.4433381840327</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>715.5664982547639</v>
+        <v>715.566498254764</v>
       </c>
       <c r="M39" s="164" t="n">
         <v>77744750.46973813</v>
@@ -4858,7 +4858,7 @@
         <v>120261388.3825528</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>139602407.1422744</v>
+        <v>139602407.1422745</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4869,25 +4869,25 @@
         <v>587.1547890814566</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>628.0986573297447</v>
+        <v>628.0986573297446</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>668.7968127405915</v>
+        <v>668.7968127405916</v>
       </c>
       <c r="W39" s="162" t="n">
         <v>710.9309353645311</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>745.2129840146542</v>
+        <v>745.2129840146544</v>
       </c>
       <c r="Y39" s="161" t="n">
         <v>582.396315117359</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>624.3667766380611</v>
+        <v>624.366776638061</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>666.1127294171489</v>
+        <v>666.112729417149</v>
       </c>
       <c r="AB39" s="162" t="n">
         <v>709.3269090097732</v>
@@ -4908,7 +4908,7 @@
         <v>120261388.3825528</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>139602407.1422744</v>
+        <v>139602407.1422745</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4921,40 +4921,40 @@
         <v>4903.098820970239</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>5104.150339822288</v>
+        <v>5104.150339822287</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>5701.495554346445</v>
+        <v>5701.495554346443</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>5996.951367971825</v>
+        <v>5996.951367971824</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>6396.60466619619</v>
+        <v>6396.604666196187</v>
       </c>
       <c r="H40" s="155" t="n">
         <v>4895.558019140841</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>5096.577036070785</v>
+        <v>5096.577036070784</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>5693.202843680533</v>
+        <v>5693.202843680531</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>5989.077941201233</v>
+        <v>5989.077941201232</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>6388.943852745718</v>
+        <v>6388.943852745715</v>
       </c>
       <c r="M40" s="158" t="n">
         <v>6887295.464618078</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>7625160.03823325</v>
+        <v>7625160.038233249</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>8953294.267540315</v>
+        <v>8953294.267540311</v>
       </c>
       <c r="P40" s="159" t="n">
         <v>10645841.53973097</v>
@@ -4974,37 +4974,37 @@
         <v>4155.478389931418</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>4641.799318003946</v>
+        <v>4641.799318003944</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>4882.340870849864</v>
+        <v>4882.340870849863</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>5207.713466417648</v>
+        <v>5207.713466417646</v>
       </c>
       <c r="Y40" s="155" t="n">
         <v>3985.8462016986</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>4149.504081860302</v>
+        <v>4149.504081860301</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>4635.257501539254</v>
+        <v>4635.257501539252</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>4876.129839468536</v>
+        <v>4876.129839468535</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>5201.670178834521</v>
+        <v>5201.670178834519</v>
       </c>
       <c r="AD40" s="158" t="n">
         <v>6887295.464618078</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>7625160.03823325</v>
+        <v>7625160.038233249</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>8953294.267540315</v>
+        <v>8953294.267540311</v>
       </c>
       <c r="AG40" s="159" t="n">
         <v>10645841.53973097</v>
@@ -5029,7 +5029,7 @@
         <v>691.0786846123509</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>736.2408368197235</v>
+        <v>736.2408368197233</v>
       </c>
       <c r="G41" s="181" t="n">
         <v>773.2320863015746</v>
@@ -5038,13 +5038,13 @@
         <v>602.7120610445617</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>643.6441539520398</v>
+        <v>643.6441539520397</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>687.947193989345</v>
+        <v>687.9471939893449</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>734.3697163592889</v>
+        <v>734.3697163592888</v>
       </c>
       <c r="L41" s="181" t="n">
         <v>772.7989943826093</v>
@@ -5062,7 +5062,7 @@
         <v>130907229.9222837</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>152304531.6492073</v>
+        <v>152304531.6492074</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>630.9483950782648</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>672.2432092862921</v>
+        <v>672.243209286292</v>
       </c>
       <c r="V41" s="186" t="n">
         <v>717.0971501414309</v>
@@ -5088,7 +5088,7 @@
         <v>625.8883325968457</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>668.2867636713224</v>
+        <v>668.2867636713222</v>
       </c>
       <c r="AA41" s="186" t="n">
         <v>714.2418655677669</v>
@@ -5112,7 +5112,7 @@
         <v>130907229.9222837</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>152304531.6492073</v>
+        <v>152304531.6492074</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -5374,7 +5374,7 @@
         <v>0.1713538103053007</v>
       </c>
       <c r="D46" s="149" t="n">
-        <v>0.1841154846545519</v>
+        <v>0.1841154846545518</v>
       </c>
       <c r="E46" s="149" t="n">
         <v>0.2012688125870582</v>
@@ -5389,16 +5389,16 @@
         <v>0.1697540772505141</v>
       </c>
       <c r="I46" s="149" t="n">
-        <v>0.1828621798541111</v>
+        <v>0.182862179854111</v>
       </c>
       <c r="J46" s="149" t="n">
-        <v>0.2003454367456158</v>
+        <v>0.2003454367456157</v>
       </c>
       <c r="K46" s="149" t="n">
-        <v>0.2210237254653181</v>
+        <v>0.221023725465318</v>
       </c>
       <c r="L46" s="150" t="n">
-        <v>0.2386276187655711</v>
+        <v>0.238627618765571</v>
       </c>
       <c r="M46" s="151" t="n">
         <v>18294.80849625192</v>
@@ -5442,13 +5442,13 @@
         <v>0.1893634639143324</v>
       </c>
       <c r="AA46" s="149" t="n">
-        <v>0.2073915493134459</v>
+        <v>0.2073915493134458</v>
       </c>
       <c r="AB46" s="149" t="n">
-        <v>0.2287188933422588</v>
+        <v>0.2287188933422587</v>
       </c>
       <c r="AC46" s="150" t="n">
-        <v>0.2468488789956131</v>
+        <v>0.246848878995613</v>
       </c>
       <c r="AD46" s="151" t="n">
         <v>18294.80849625192</v>
@@ -5476,13 +5476,13 @@
         <v>0.02957062747023871</v>
       </c>
       <c r="D47" s="156" t="n">
-        <v>0.02864489004090478</v>
+        <v>0.02864489004090477</v>
       </c>
       <c r="E47" s="156" t="n">
         <v>0.02778923529773249</v>
       </c>
       <c r="F47" s="156" t="n">
-        <v>0.02692684183910093</v>
+        <v>0.02692684183910092</v>
       </c>
       <c r="G47" s="157" t="n">
         <v>0.02544520057998245</v>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="T47" s="155" t="n">
-        <v>0.02993332896369404</v>
+        <v>0.02993332896369403</v>
       </c>
       <c r="U47" s="156" t="n">
         <v>0.02899623680918543</v>
@@ -5538,16 +5538,16 @@
         <v>0.02575730123665327</v>
       </c>
       <c r="Y47" s="155" t="n">
-        <v>0.02962217308290659</v>
+        <v>0.02962217308290658</v>
       </c>
       <c r="Z47" s="156" t="n">
-        <v>0.02876347091282912</v>
+        <v>0.02876347091282911</v>
       </c>
       <c r="AA47" s="156" t="n">
         <v>0.02796737827743326</v>
       </c>
       <c r="AB47" s="156" t="n">
-        <v>0.02715809378616574</v>
+        <v>0.02715809378616573</v>
       </c>
       <c r="AC47" s="157" t="n">
         <v>0.0257210849011311</v>
@@ -5581,7 +5581,7 @@
         <v>0.1572997009424719</v>
       </c>
       <c r="E48" s="162" t="n">
-        <v>0.1716624177706212</v>
+        <v>0.1716624177706211</v>
       </c>
       <c r="F48" s="162" t="n">
         <v>0.1885096345126199</v>
@@ -5596,10 +5596,10 @@
         <v>0.15619767955492</v>
       </c>
       <c r="J48" s="162" t="n">
-        <v>0.1708412552676225</v>
+        <v>0.1708412552676224</v>
       </c>
       <c r="K48" s="162" t="n">
-        <v>0.1879973077606336</v>
+        <v>0.1879973077606335</v>
       </c>
       <c r="L48" s="163" t="n">
         <v>0.2025429900178021</v>
@@ -5631,10 +5631,10 @@
         <v>0.162096711578104</v>
       </c>
       <c r="V48" s="162" t="n">
-        <v>0.1769044378751111</v>
+        <v>0.176904437875111</v>
       </c>
       <c r="W48" s="162" t="n">
-        <v>0.1942692581774165</v>
+        <v>0.1942692581774164</v>
       </c>
       <c r="X48" s="163" t="n">
         <v>0.2088583338527553</v>
@@ -5646,10 +5646,10 @@
         <v>0.1611090853595726</v>
       </c>
       <c r="AA48" s="162" t="n">
-        <v>0.1761672373232127</v>
+        <v>0.1761672373232126</v>
       </c>
       <c r="AB48" s="162" t="n">
-        <v>0.1938072898705684</v>
+        <v>0.1938072898705683</v>
       </c>
       <c r="AC48" s="163" t="n">
         <v>0.2087463013240246</v>
@@ -5680,10 +5680,10 @@
         <v>0.1638090623679853</v>
       </c>
       <c r="D49" s="156" t="n">
-        <v>0.1633912871997914</v>
+        <v>0.1633912871997915</v>
       </c>
       <c r="E49" s="156" t="n">
-        <v>0.1639670431477857</v>
+        <v>0.1639670431477858</v>
       </c>
       <c r="F49" s="156" t="n">
         <v>0.1645350746210813</v>
@@ -5698,7 +5698,7 @@
         <v>0.1629314776199473</v>
       </c>
       <c r="J49" s="156" t="n">
-        <v>0.1638004206071732</v>
+        <v>0.1638004206071733</v>
       </c>
       <c r="K49" s="156" t="n">
         <v>0.1645350746210813</v>
@@ -5733,7 +5733,7 @@
         <v>0.2003990076246396</v>
       </c>
       <c r="V49" s="156" t="n">
-        <v>0.2011051708637538</v>
+        <v>0.2011051708637539</v>
       </c>
       <c r="W49" s="156" t="n">
         <v>0.20180186005385</v>
@@ -5785,10 +5785,10 @@
         <v>0.1576573255203869</v>
       </c>
       <c r="E50" s="162" t="n">
-        <v>0.171205818646843</v>
+        <v>0.1712058186468429</v>
       </c>
       <c r="F50" s="162" t="n">
-        <v>0.1870596718200305</v>
+        <v>0.1870596718200304</v>
       </c>
       <c r="G50" s="163" t="n">
         <v>0.2001022769274538</v>
@@ -5800,7 +5800,7 @@
         <v>0.1565914424743424</v>
       </c>
       <c r="J50" s="162" t="n">
-        <v>0.1704249750970716</v>
+        <v>0.1704249750970715</v>
       </c>
       <c r="K50" s="162" t="n">
         <v>0.1865819540120806</v>
@@ -5821,7 +5821,7 @@
         <v>32928.05663992357</v>
       </c>
       <c r="Q50" s="166" t="n">
-        <v>39017.05105688934</v>
+        <v>39017.05105688935</v>
       </c>
       <c r="S50" s="42" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>0.1640039067332622</v>
       </c>
       <c r="V50" s="162" t="n">
-        <v>0.1781224942860637</v>
+        <v>0.1781224942860636</v>
       </c>
       <c r="W50" s="162" t="n">
         <v>0.1946557778984808</v>
@@ -5847,7 +5847,7 @@
         <v>0.1520447767667079</v>
       </c>
       <c r="Z50" s="162" t="n">
-        <v>0.1630294690302738</v>
+        <v>0.1630294690302737</v>
       </c>
       <c r="AA50" s="162" t="n">
         <v>0.1774076349934721</v>
@@ -5871,7 +5871,7 @@
         <v>32928.05663992357</v>
       </c>
       <c r="AH50" s="166" t="n">
-        <v>39017.05105688934</v>
+        <v>39017.05105688935</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -5992,7 +5992,7 @@
         <v>0.1695727782879473</v>
       </c>
       <c r="F52" s="180" t="n">
-        <v>0.1851920630343872</v>
+        <v>0.1851920630343871</v>
       </c>
       <c r="G52" s="181" t="n">
         <v>0.1980849516647367</v>
@@ -6004,7 +6004,7 @@
         <v>0.1550615716477642</v>
       </c>
       <c r="J52" s="180" t="n">
-        <v>0.168804391739571</v>
+        <v>0.1688043917395709</v>
       </c>
       <c r="K52" s="180" t="n">
         <v>0.1847214063675408</v>
@@ -6025,7 +6025,7 @@
         <v>32928.05663992357</v>
       </c>
       <c r="Q52" s="184" t="n">
-        <v>39017.05105688934</v>
+        <v>39017.05105688935</v>
       </c>
       <c r="S52" s="51" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>0.1619514259881502</v>
       </c>
       <c r="V52" s="186" t="n">
-        <v>0.1759570346465849</v>
+        <v>0.1759570346465848</v>
       </c>
       <c r="W52" s="186" t="n">
         <v>0.1921785947737192</v>
@@ -6054,7 +6054,7 @@
         <v>0.1609982709389989</v>
       </c>
       <c r="AA52" s="186" t="n">
-        <v>0.1752564218961996</v>
+        <v>0.1752564218961995</v>
       </c>
       <c r="AB52" s="186" t="n">
         <v>0.19174739935715</v>
@@ -6075,7 +6075,7 @@
         <v>32928.05663992357</v>
       </c>
       <c r="AH52" s="190" t="n">
-        <v>39017.05105688934</v>
+        <v>39017.05105688935</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,28 +6334,28 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.009767608927579389</v>
+        <v>0.009767608927579382</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.008745544064354753</v>
+        <v>0.008745544064354752</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.007944794222634</v>
+        <v>0.007944794222633994</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.0002873393007558205</v>
+        <v>0.0002873393007558204</v>
       </c>
       <c r="G57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.00967642001943759</v>
+        <v>0.009676420019437583</v>
       </c>
       <c r="I57" s="149" t="n">
         <v>0.00868601168782006</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.007908345301630709</v>
+        <v>0.007908345301630704</v>
       </c>
       <c r="K57" s="149" t="n">
         <v>0.0002866104039218012</v>
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>1042.851247240796</v>
+        <v>1042.851247240795</v>
       </c>
       <c r="N57" s="152" t="n">
         <v>1026.036120231114</v>
@@ -6387,13 +6387,13 @@
         <v>0.01010340758977952</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.009046205364248796</v>
+        <v>0.009046205364248794</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.008217926704820409</v>
+        <v>0.008217926704820402</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0002972176807674206</v>
+        <v>0.0002972176807674205</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
@@ -6405,7 +6405,7 @@
         <v>0.008994824747896087</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.008186480367373752</v>
+        <v>0.008186480367373745</v>
       </c>
       <c r="AB57" s="149" t="n">
         <v>0.0002965890393321528</v>
@@ -6414,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>1042.851247240796</v>
+        <v>1042.851247240795</v>
       </c>
       <c r="AE57" s="152" t="n">
         <v>1026.036120231114</v>
@@ -6538,13 +6538,13 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.008044367065170579</v>
+        <v>0.008044367065170574</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.007237100498823965</v>
+        <v>0.007237100498823964</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.006588918688660565</v>
+        <v>0.006588918688660561</v>
       </c>
       <c r="F59" s="162" t="n">
         <v>0.0002385149967107674</v>
@@ -6553,13 +6553,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.007967889013713697</v>
+        <v>0.007967889013713692</v>
       </c>
       <c r="I59" s="162" t="n">
         <v>0.007186398307492506</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.006557400007794348</v>
+        <v>0.006557400007794343</v>
       </c>
       <c r="K59" s="162" t="n">
         <v>0.0002378667666408254</v>
@@ -6568,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>1042.851247240796</v>
+        <v>1042.851247240795</v>
       </c>
       <c r="N59" s="165" t="n">
         <v>1026.036120231114</v>
@@ -6588,37 +6588,37 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.00828897677904139</v>
+        <v>0.008288976779041385</v>
       </c>
       <c r="U59" s="162" t="n">
         <v>0.007457803067589135</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.006790123149609961</v>
+        <v>0.006790123149609956</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.0002458024577629093</v>
+        <v>0.0002458024577629092</v>
       </c>
       <c r="X59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.008220499345043562</v>
+        <v>0.008220499345043557</v>
       </c>
       <c r="Z59" s="162" t="n">
         <v>0.007412364009816231</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.006761827180365342</v>
+        <v>0.006761827180365337</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.0002452179445656224</v>
+        <v>0.0002452179445656223</v>
       </c>
       <c r="AC59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>1042.851247240796</v>
+        <v>1042.851247240795</v>
       </c>
       <c r="AE59" s="165" t="n">
         <v>1026.036120231114</v>
@@ -6742,37 +6742,37 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.00757174925280553</v>
+        <v>0.007571749252805525</v>
       </c>
       <c r="D61" s="162" t="n">
         <v>0.006812225121230737</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.006197970275186209</v>
+        <v>0.006197970275186206</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.0002240897956468783</v>
+        <v>0.0002240897956468782</v>
       </c>
       <c r="G61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.007501887019534687</v>
+        <v>0.007501887019534682</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.006766169314825349</v>
+        <v>0.006766169314825348</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.006169702280854564</v>
+        <v>0.006169702280854558</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>0.0002235175093549224</v>
+        <v>0.0002235175093549223</v>
       </c>
       <c r="L61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>1042.851247240796</v>
+        <v>1042.851247240795</v>
       </c>
       <c r="N61" s="165" t="n">
         <v>1026.036120231114</v>
@@ -6792,13 +6792,13 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.007875967192863329</v>
+        <v>0.007875967192863324</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.007086454941060387</v>
+        <v>0.007086454941060386</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.006448366846715264</v>
+        <v>0.00644836684671526</v>
       </c>
       <c r="W61" s="162" t="n">
         <v>0.0002331896184054129</v>
@@ -6807,13 +6807,13 @@
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.007812138053552454</v>
+        <v>0.007812138053552449</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.007044350402134195</v>
+        <v>0.007044350402134194</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.006422487605685714</v>
+        <v>0.006422487605685711</v>
       </c>
       <c r="AB61" s="162" t="n">
         <v>0.0002326634881233111</v>
@@ -6822,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>1042.851247240796</v>
+        <v>1042.851247240795</v>
       </c>
       <c r="AE61" s="165" t="n">
         <v>1026.036120231114</v>
@@ -6946,28 +6946,28 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.007495305627883397</v>
+        <v>0.007495305627883393</v>
       </c>
       <c r="D63" s="180" t="n">
         <v>0.006745320756196923</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.006138851165318262</v>
+        <v>0.006138851165318258</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.0002218524771107601</v>
+        <v>0.00022185247711076</v>
       </c>
       <c r="G63" s="181" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.007426726101776037</v>
+        <v>0.007426726101776032</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.006700065031737619</v>
+        <v>0.006700065031737618</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.006111034137694257</v>
+        <v>0.006111034137694251</v>
       </c>
       <c r="K63" s="180" t="n">
         <v>0.0002212886497755186</v>
@@ -6976,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>1042.851247240796</v>
+        <v>1042.851247240795</v>
       </c>
       <c r="N63" s="183" t="n">
         <v>1026.036120231114</v>
@@ -6996,13 +6996,13 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.00777465927341878</v>
+        <v>0.007774659273418775</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.006997769173706772</v>
+        <v>0.00699776917370677</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.006369973164866808</v>
+        <v>0.006369973164866804</v>
       </c>
       <c r="W63" s="186" t="n">
         <v>0.0002302220548744462</v>
@@ -7011,13 +7011,13 @@
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.007712308276091395</v>
+        <v>0.00771230827609139</v>
       </c>
       <c r="Z63" s="186" t="n">
         <v>0.006956584238285443</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.006344609675263327</v>
+        <v>0.006344609675263323</v>
       </c>
       <c r="AB63" s="186" t="n">
         <v>0.0002297055004945378</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>1042.851247240796</v>
+        <v>1042.851247240795</v>
       </c>
       <c r="AE63" s="189" t="n">
         <v>1026.036120231114</v>
@@ -7297,43 +7297,43 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.004145782646036412</v>
+        <v>0.004145782646036411</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.005862050084171071</v>
+        <v>0.00586205008417107</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.007609732210569718</v>
+        <v>0.007609732210569713</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.009245243871474511</v>
+        <v>0.009245243871474509</v>
       </c>
       <c r="G68" s="150" t="n">
         <v>0.0106505620170085</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.004107078251164722</v>
+        <v>0.004107078251164721</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.005822146131905999</v>
+        <v>0.005822146131905998</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.007574820478380474</v>
+        <v>0.007574820478380468</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.009221791357426042</v>
+        <v>0.00922179135742604</v>
       </c>
       <c r="L68" s="150" t="n">
         <v>0.01064602120713725</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>442.6297812764452</v>
+        <v>442.6297812764451</v>
       </c>
       <c r="N68" s="152" t="n">
         <v>687.7416751552466</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>968.0315152083142</v>
+        <v>968.0315152083136</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>1269.203770234304</v>
@@ -7347,16 +7347,16 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.004288309673544727</v>
+        <v>0.004288309673544726</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.006063580324643411</v>
+        <v>0.00606358032464341</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.007871345663253667</v>
+        <v>0.007871345663253662</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.009563084250504153</v>
+        <v>0.009563084250504152</v>
       </c>
       <c r="X68" s="150" t="n">
         <v>0.01101671554583097</v>
@@ -7365,25 +7365,25 @@
         <v>0.004254890974917171</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.006029140415107905</v>
+        <v>0.006029140415107904</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.007841225536757436</v>
+        <v>0.007841225536757429</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.009542857489453797</v>
+        <v>0.009542857489453795</v>
       </c>
       <c r="AC68" s="150" t="n">
         <v>0.01101280067386949</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>442.6297812764452</v>
+        <v>442.6297812764451</v>
       </c>
       <c r="AE68" s="152" t="n">
         <v>687.7416751552466</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>968.0315152083142</v>
+        <v>968.0315152083136</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>1269.203770234304</v>
@@ -7504,40 +7504,40 @@
         <v>0.003414366568563664</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.004850955558179512</v>
+        <v>0.004850955558179511</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.006311039074502526</v>
+        <v>0.006311039074502521</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.007674304579271227</v>
+        <v>0.007674304579271225</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.008849528788739895</v>
+        <v>0.008849528788739893</v>
       </c>
       <c r="H70" s="161" t="n">
         <v>0.003381906077886424</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.004816970390101331</v>
+        <v>0.00481697039010133</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.006280849655582271</v>
+        <v>0.006280849655582265</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.007653447546955522</v>
+        <v>0.007653447546955519</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.008844306853956164</v>
+        <v>0.008844306853956162</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>442.6297812764452</v>
+        <v>442.6297812764451</v>
       </c>
       <c r="N70" s="165" t="n">
         <v>687.7416751552466</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>968.0315152083142</v>
+        <v>968.0315152083136</v>
       </c>
       <c r="P70" s="165" t="n">
         <v>1269.203770234304</v>
@@ -7557,37 +7557,37 @@
         <v>0.004998890266676356</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.006503757982568757</v>
+        <v>0.006503757982568752</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.007908781222228531</v>
+        <v>0.007908781222228529</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.009120074673714612</v>
+        <v>0.009120074673714611</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.003489124490867706</v>
+        <v>0.003489124490867705</v>
       </c>
       <c r="Z70" s="162" t="n">
         <v>0.004968432924001936</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.006476655361335772</v>
+        <v>0.006476655361335766</v>
       </c>
       <c r="AB70" s="162" t="n">
         <v>0.007889974302879878</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.009115182625554212</v>
+        <v>0.00911518262555421</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>442.6297812764452</v>
+        <v>442.6297812764451</v>
       </c>
       <c r="AE70" s="165" t="n">
         <v>687.7416751552466</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>968.0315152083142</v>
+        <v>968.0315152083136</v>
       </c>
       <c r="AG70" s="165" t="n">
         <v>1269.203770234304</v>
@@ -7645,7 +7645,7 @@
         <v>214.9713475067104</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>276.4336872430842</v>
+        <v>276.4336872430843</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>214.9713475067104</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>276.4336872430842</v>
+        <v>276.4336872430843</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7711,28 +7711,28 @@
         <v>0.005332253555395017</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.006937094080221839</v>
+        <v>0.006937094080221837</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.008431390697727303</v>
+        <v>0.008431390697727302</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.009719971482341189</v>
+        <v>0.009719971482341187</v>
       </c>
       <c r="H72" s="161" t="n">
         <v>0.00371654104665275</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.005296203478792829</v>
+        <v>0.005296203478792828</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.006905455055277998</v>
+        <v>0.006905455055277994</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.008409858394997922</v>
+        <v>0.008409858394997921</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.009714590417804616</v>
+        <v>0.009714590417804614</v>
       </c>
       <c r="M72" s="164" t="n">
         <v>516.6432733298925</v>
@@ -7758,10 +7758,10 @@
         <v>0.003901865661019057</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.00554690631653539</v>
+        <v>0.005546906316535389</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.007217351083230759</v>
+        <v>0.007217351083230755</v>
       </c>
       <c r="W72" s="162" t="n">
         <v>0.00877377202185586</v>
@@ -7773,10 +7773,10 @@
         <v>0.003870243801665049</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.005513949085470352</v>
+        <v>0.005513949085470351</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.007188385676528912</v>
+        <v>0.007188385676528909</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.00875397634149701</v>
@@ -7915,28 +7915,28 @@
         <v>0.005279884317447909</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.006870924865320174</v>
+        <v>0.006870924865320172</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.008347211466634582</v>
+        <v>0.008347211466634578</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.009621979873623386</v>
+        <v>0.009621979873623385</v>
       </c>
       <c r="H74" s="179" t="n">
         <v>0.003679305263812149</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.005244460503149989</v>
+        <v>0.005244460503149988</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.006839790586017092</v>
+        <v>0.006839790586017088</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.008325997432609708</v>
+        <v>0.008325997432609707</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.009616590545113178</v>
+        <v>0.009616590545113176</v>
       </c>
       <c r="M74" s="182" t="n">
         <v>516.6432733298925</v>
@@ -7962,31 +7962,31 @@
         <v>0.003851676283334986</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.005477487735988126</v>
+        <v>0.005477487735988124</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.007129608754350134</v>
+        <v>0.007129608754350131</v>
       </c>
       <c r="W74" s="186" t="n">
         <v>0.008662117283282512</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>0.009987040572517005</v>
+        <v>0.009987040572517003</v>
       </c>
       <c r="Y74" s="185" t="n">
         <v>0.003820786716448209</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.005445250322452765</v>
+        <v>0.005445250322452764</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.007101220603750818</v>
+        <v>0.007101220603750814</v>
       </c>
       <c r="AB74" s="186" t="n">
         <v>0.008642681896762313</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.009981880715822322</v>
+        <v>0.00998188071582232</v>
       </c>
       <c r="AD74" s="188" t="n">
         <v>516.6432733298925</v>
@@ -8260,49 +8260,49 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>466.6960857993933</v>
+        <v>466.6960857993932</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>503.0285132179618</v>
+        <v>503.0285132179617</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>538.7660517631343</v>
+        <v>538.7660517631344</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>575.9169426275225</v>
+        <v>575.9169426275224</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>606.773738726329</v>
+        <v>606.7737387263292</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>462.3390822774839</v>
+        <v>462.3390822774838</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>499.6043142617602</v>
+        <v>499.6043142617601</v>
       </c>
       <c r="J79" s="149" t="n">
         <v>536.2943148358237</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>574.4560076456562</v>
+        <v>574.456007645656</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>606.5150440041137</v>
+        <v>606.5150440041139</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>49827403.89862307</v>
+        <v>49827403.89862306</v>
       </c>
       <c r="N79" s="152" t="n">
         <v>59015816.54266846</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>68536251.07946101</v>
+        <v>68536251.07946102</v>
       </c>
       <c r="P79" s="152" t="n">
         <v>79062917.65650159</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>92225893.79799461</v>
+        <v>92225893.79799464</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>482.7405366396579</v>
+        <v>482.7405366396578</v>
       </c>
       <c r="U79" s="149" t="n">
         <v>520.3220292708179</v>
@@ -8319,13 +8319,13 @@
         <v>557.288181463688</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>595.716275330807</v>
+        <v>595.7162753308069</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>627.6338910146917</v>
+        <v>627.6338910146918</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>478.9785507437257</v>
+        <v>478.9785507437256</v>
       </c>
       <c r="Z79" s="149" t="n">
         <v>517.366705409668</v>
@@ -8334,25 +8334,25 @@
         <v>555.155688337525</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>594.4562832153669</v>
+        <v>594.4562832153667</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>627.4108566346365</v>
+        <v>627.4108566346366</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>49827403.89862307</v>
+        <v>49827403.89862306</v>
       </c>
       <c r="AE79" s="152" t="n">
         <v>59015816.54266846</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>68536251.07946101</v>
+        <v>68536251.07946102</v>
       </c>
       <c r="AG79" s="152" t="n">
         <v>79062917.65650159</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>92225893.79799461</v>
+        <v>92225893.79799464</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>912.2469823518217</v>
+        <v>912.2469823518215</v>
       </c>
       <c r="D80" s="156" t="n">
         <v>971.1785955587135</v>
@@ -8374,10 +8374,10 @@
         <v>1083.257857375969</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>1127.725453169714</v>
+        <v>1127.725453169713</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>902.8459456136087</v>
+        <v>902.8459456136086</v>
       </c>
       <c r="I80" s="156" t="n">
         <v>963.4498648032685</v>
@@ -8412,13 +8412,13 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>923.4362390976288</v>
+        <v>923.4362390976286</v>
       </c>
       <c r="U80" s="156" t="n">
         <v>983.0906839097471</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1040.936319718564</v>
+        <v>1040.936319718563</v>
       </c>
       <c r="W80" s="156" t="n">
         <v>1096.544665140292</v>
@@ -8427,7 +8427,7 @@
         <v>1141.557682684758</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>913.8371525183853</v>
+        <v>913.8371525183852</v>
       </c>
       <c r="Z80" s="156" t="n">
         <v>975.1989707282868</v>
@@ -8436,7 +8436,7 @@
         <v>1034.915386898416</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>1092.561046000477</v>
+        <v>1092.561046000476</v>
       </c>
       <c r="AC80" s="157" t="n">
         <v>1139.952583001598</v>
@@ -8467,13 +8467,13 @@
         <v>545.302013049922</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>583.775688489523</v>
+        <v>583.7756884895228</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>622.3149392353804</v>
+        <v>622.3149392353803</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>662.1236223647418</v>
+        <v>662.1236223647415</v>
       </c>
       <c r="G81" s="163" t="n">
         <v>694.8678079911891</v>
@@ -8482,13 +8482,13 @@
         <v>540.1178096097117</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>579.6858314179983</v>
+        <v>579.6858314179982</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>619.3380401575703</v>
+        <v>619.3380401575702</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>660.3241194070464</v>
+        <v>660.3241194070461</v>
       </c>
       <c r="L81" s="163" t="n">
         <v>694.4577800153198</v>
@@ -8520,10 +8520,10 @@
         <v>601.5785080100243</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>641.3184431191207</v>
+        <v>641.3184431191206</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>682.3537973064766</v>
+        <v>682.3537973064764</v>
       </c>
       <c r="X81" s="163" t="n">
         <v>716.1111567096679</v>
@@ -8535,13 +8535,13 @@
         <v>597.9131979538764</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>638.6459250303217</v>
+        <v>638.6459250303216</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>680.7311739878394</v>
+        <v>680.7311739878392</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>715.7270315361184</v>
+        <v>715.7270315361185</v>
       </c>
       <c r="AD81" s="164" t="n">
         <v>70691563.40393442</v>
@@ -8566,46 +8566,46 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>874.3488589583443</v>
+        <v>874.3488589583444</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>927.6263505918112</v>
+        <v>927.6263505918113</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>971.1213793260646</v>
+        <v>971.1213793260647</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>1013.652199235176</v>
+        <v>1013.652199235175</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>1039.373711732197</v>
+        <v>1039.373711732196</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>870.2273947436233</v>
+        <v>870.2273947436234</v>
       </c>
       <c r="I82" s="156" t="n">
-        <v>925.0158596052482</v>
+        <v>925.0158596052484</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>970.1345303327543</v>
+        <v>970.1345303327544</v>
       </c>
       <c r="K82" s="156" t="n">
         <v>1013.652199235176</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>1039.373711732197</v>
+        <v>1039.373711732196</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>7075043.191541074</v>
+        <v>7075043.191541075</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>8202451.954759018</v>
+        <v>8202451.954759019</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>9395764.189946579</v>
+        <v>9395764.189946581</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>10791481.82400831</v>
+        <v>10791481.8240083</v>
       </c>
       <c r="Q82" s="160" t="n">
         <v>12533041.65408611</v>
@@ -8622,40 +8622,40 @@
         <v>1137.731413289841</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>1191.07795792102</v>
+        <v>1191.077957921021</v>
       </c>
       <c r="W82" s="156" t="n">
-        <v>1243.241902824804</v>
+        <v>1243.241902824803</v>
       </c>
       <c r="X82" s="157" t="n">
         <v>1274.789273968926</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>1066.916103983904</v>
+        <v>1066.916103983905</v>
       </c>
       <c r="Z82" s="156" t="n">
         <v>1134.26585151107</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>1189.767670197836</v>
+        <v>1189.767670197837</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>1243.241902824804</v>
+        <v>1243.241902824803</v>
       </c>
       <c r="AC82" s="157" t="n">
         <v>1274.789273968926</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>7075043.191541074</v>
+        <v>7075043.191541075</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>8202451.954759018</v>
+        <v>8202451.954759019</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>9395764.189946579</v>
+        <v>9395764.189946581</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>10791481.82400831</v>
+        <v>10791481.8240083</v>
       </c>
       <c r="AH82" s="160" t="n">
         <v>12533041.65408611</v>
@@ -8671,16 +8671,16 @@
         <v>564.6339753061175</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>603.9624580279772</v>
+        <v>603.9624580279773</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>643.0111005945686</v>
+        <v>643.0111005945687</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>683.3837966556187</v>
+        <v>683.3837966556182</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>716.1726840493158</v>
+        <v>716.1726840493159</v>
       </c>
       <c r="H83" s="161" t="n">
         <v>559.4242689122002</v>
@@ -8692,7 +8692,7 @@
         <v>640.0784253251238</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>681.6385535139494</v>
+        <v>681.6385535139491</v>
       </c>
       <c r="L83" s="163" t="n">
         <v>715.7762043436705</v>
@@ -8701,7 +8701,7 @@
         <v>77766606.59547549</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>90966943.42484038</v>
+        <v>90966943.42484039</v>
       </c>
       <c r="O83" s="165" t="n">
         <v>104850802.0138538</v>
@@ -8721,13 +8721,13 @@
         <v>587.3198539741976</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>628.2752945977355</v>
+        <v>628.2752945977354</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>668.9886009528076</v>
+        <v>668.9886009528077</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>711.1345981040701</v>
+        <v>711.1345981040699</v>
       </c>
       <c r="X83" s="163" t="n">
         <v>745.4313783926209</v>
@@ -8736,13 +8736,13 @@
         <v>582.5600422759809</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>624.5423644065789</v>
+        <v>624.5423644065788</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>666.3037479254247</v>
+        <v>666.3037479254248</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>709.53011223857</v>
+        <v>709.5301122385698</v>
       </c>
       <c r="AC83" s="163" t="n">
         <v>745.0524998937453</v>
@@ -8751,7 +8751,7 @@
         <v>77766606.59547549</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>90966943.42484038</v>
+        <v>90966943.42484039</v>
       </c>
       <c r="AF83" s="165" t="n">
         <v>104850802.0138538</v>
@@ -8773,40 +8773,40 @@
         <v>4903.098820970239</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>5104.150339822288</v>
+        <v>5104.150339822287</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>5701.495554346445</v>
+        <v>5701.495554346443</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>5996.951367971825</v>
+        <v>5996.951367971824</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>6396.60466619619</v>
+        <v>6396.604666196187</v>
       </c>
       <c r="H84" s="155" t="n">
         <v>4895.558019140841</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>5096.577036070785</v>
+        <v>5096.577036070784</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>5693.202843680533</v>
+        <v>5693.202843680531</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>5989.077941201233</v>
+        <v>5989.077941201232</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>6388.943852745718</v>
+        <v>6388.943852745715</v>
       </c>
       <c r="M84" s="158" t="n">
         <v>6887295.464618078</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>7625160.03823325</v>
+        <v>7625160.038233249</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>8953294.267540315</v>
+        <v>8953294.267540311</v>
       </c>
       <c r="P84" s="159" t="n">
         <v>10645841.53973097</v>
@@ -8826,37 +8826,37 @@
         <v>4155.478389931418</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>4641.799318003946</v>
+        <v>4641.799318003944</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>4882.340870849864</v>
+        <v>4882.340870849863</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>5207.713466417648</v>
+        <v>5207.713466417646</v>
       </c>
       <c r="Y84" s="155" t="n">
         <v>3985.8462016986</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>4149.504081860302</v>
+        <v>4149.504081860301</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>4635.257501539254</v>
+        <v>4635.257501539252</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>4876.129839468536</v>
+        <v>4876.129839468535</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>5201.670178834521</v>
+        <v>5201.670178834519</v>
       </c>
       <c r="AD84" s="158" t="n">
         <v>6887295.464618078</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>7625160.03823325</v>
+        <v>7625160.038233249</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>8953294.267540315</v>
+        <v>8953294.267540311</v>
       </c>
       <c r="AG84" s="159" t="n">
         <v>10645841.53973097</v>
@@ -8875,16 +8875,16 @@
         <v>608.4346834815655</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>648.159795521415</v>
+        <v>648.1597955214152</v>
       </c>
       <c r="E85" s="180" t="n">
         <v>691.2612671666695</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>736.4345979467018</v>
+        <v>736.4345979467014</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>773.4397932331129</v>
+        <v>773.4397932331131</v>
       </c>
       <c r="H85" s="179" t="n">
         <v>602.8677107212791</v>
@@ -8893,19 +8893,19 @@
         <v>643.8111600492224</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>688.1289492058083</v>
+        <v>688.1289492058082</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>734.5629850517389</v>
+        <v>734.5629850517387</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>773.0065849762523</v>
+        <v>773.0065849762524</v>
       </c>
       <c r="M85" s="182" t="n">
         <v>84653902.06009357</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>98592103.46307363</v>
+        <v>98592103.46307364</v>
       </c>
       <c r="O85" s="183" t="n">
         <v>113804096.2813942</v>
@@ -8931,22 +8931,22 @@
         <v>717.2866067579968</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>764.2172340283653</v>
+        <v>764.2172340283651</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>802.7843226520348</v>
+        <v>802.7843226520349</v>
       </c>
       <c r="Y85" s="185" t="n">
         <v>626.0499675182724</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>668.4601637768221</v>
+        <v>668.460163776822</v>
       </c>
       <c r="AA85" s="186" t="n">
         <v>714.4305678199422</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>762.5025427071794</v>
+        <v>762.5025427071791</v>
       </c>
       <c r="AC85" s="187" t="n">
         <v>802.36955993714</v>
@@ -8955,7 +8955,7 @@
         <v>84653902.06009357</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>98592103.46307363</v>
+        <v>98592103.46307364</v>
       </c>
       <c r="AF85" s="189" t="n">
         <v>113804096.2813942</v>
@@ -9314,13 +9314,13 @@
         <v>107772.4246307993</v>
       </c>
       <c r="N90" s="75" t="n">
-        <v>118125.1139311579</v>
+        <v>118125.113931158</v>
       </c>
       <c r="O90" s="75" t="n">
         <v>127795.9679666604</v>
       </c>
       <c r="P90" s="75" t="n">
-        <v>137630.9353618428</v>
+        <v>137630.9353618429</v>
       </c>
       <c r="Q90" s="76" t="n">
         <v>152058.7077100912</v>
@@ -9340,7 +9340,7 @@
         <v>122981.7056221328</v>
       </c>
       <c r="W90" s="75" t="n">
-        <v>132719.082775768</v>
+        <v>132719.0827757681</v>
       </c>
       <c r="X90" s="76" t="n">
         <v>146942.1825658484</v>
@@ -9367,7 +9367,7 @@
         <v>114069.6065780611</v>
       </c>
       <c r="AF90" s="75" t="n">
-        <v>123454.1093953308</v>
+        <v>123454.1093953309</v>
       </c>
       <c r="AG90" s="75" t="n">
         <v>133000.3902538578</v>
@@ -9413,10 +9413,10 @@
         <v>26177.35715783279</v>
       </c>
       <c r="F91" s="80" t="n">
-        <v>28101.74915693515</v>
+        <v>28101.74915693516</v>
       </c>
       <c r="G91" s="81" t="n">
-        <v>30933.40129649007</v>
+        <v>30933.40129649008</v>
       </c>
       <c r="H91" s="79" t="n">
         <v>238.1499839334398</v>
@@ -9437,7 +9437,7 @@
         <v>23109.32402884223</v>
       </c>
       <c r="N91" s="80" t="n">
-        <v>24649.62194193909</v>
+        <v>24649.6219419391</v>
       </c>
       <c r="O91" s="80" t="n">
         <v>26328.32544767897</v>
@@ -9446,7 +9446,7 @@
         <v>28203.3193903418</v>
       </c>
       <c r="Q91" s="81" t="n">
-        <v>30976.57744483274</v>
+        <v>30976.57744483275</v>
       </c>
       <c r="S91" s="32" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>22594.04452840141</v>
       </c>
       <c r="U91" s="80" t="n">
-        <v>24157.15591258024</v>
+        <v>24157.15591258025</v>
       </c>
       <c r="V91" s="80" t="n">
         <v>25860.16669273701</v>
@@ -9484,7 +9484,7 @@
         <v>43.0277284640058</v>
       </c>
       <c r="AD91" s="79" t="n">
-        <v>22831.37586145753</v>
+        <v>22831.37586145754</v>
       </c>
       <c r="AE91" s="80" t="n">
         <v>24352.64560387835</v>
@@ -9496,7 +9496,7 @@
         <v>27862.46195733875</v>
       </c>
       <c r="AH91" s="81" t="n">
-        <v>30601.60967687896</v>
+        <v>30601.60967687897</v>
       </c>
       <c r="AJ91" s="120" t="n">
         <v>88.90947196516059</v>
@@ -9533,7 +9533,7 @@
         <v>153387.0260951633</v>
       </c>
       <c r="F92" s="86" t="n">
-        <v>165383.5545780268</v>
+        <v>165383.5545780269</v>
       </c>
       <c r="G92" s="87" t="n">
         <v>182927.279593835</v>
@@ -9557,13 +9557,13 @@
         <v>130881.7486596416</v>
       </c>
       <c r="N92" s="86" t="n">
-        <v>142774.735873097</v>
+        <v>142774.7358730971</v>
       </c>
       <c r="O92" s="86" t="n">
         <v>154124.2934143394</v>
       </c>
       <c r="P92" s="86" t="n">
-        <v>165834.2547521846</v>
+        <v>165834.2547521847</v>
       </c>
       <c r="Q92" s="87" t="n">
         <v>183035.2851549239</v>
@@ -9583,10 +9583,10 @@
         <v>148841.8723148698</v>
       </c>
       <c r="W92" s="86" t="n">
-        <v>160480.3236517736</v>
+        <v>160480.3236517737</v>
       </c>
       <c r="X92" s="87" t="n">
-        <v>177500.7645142633</v>
+        <v>177500.7645142634</v>
       </c>
       <c r="Y92" s="85" t="n">
         <v>1048.022775568631</v>
@@ -9613,10 +9613,10 @@
         <v>149464.7254178835</v>
       </c>
       <c r="AG92" s="86" t="n">
-        <v>160862.8522111965</v>
+        <v>160862.8522111966</v>
       </c>
       <c r="AH92" s="87" t="n">
-        <v>177596.0278045541</v>
+        <v>177596.0278045542</v>
       </c>
       <c r="AJ92" s="126" t="n">
         <v>39.60477259371297</v>
@@ -9698,7 +9698,7 @@
         <v>8680.114303973094</v>
       </c>
       <c r="X93" s="81" t="n">
-        <v>9831.461489368954</v>
+        <v>9831.461489368956</v>
       </c>
       <c r="Y93" s="79" t="n">
         <v>33.82845994569738</v>
@@ -9728,7 +9728,7 @@
         <v>8680.114303973094</v>
       </c>
       <c r="AH93" s="81" t="n">
-        <v>9831.461489368954</v>
+        <v>9831.461489368956</v>
       </c>
       <c r="AJ93" s="120" t="n">
         <v>73.37968397291196</v>
@@ -9765,7 +9765,7 @@
         <v>163062.1958421902</v>
       </c>
       <c r="F94" s="86" t="n">
-        <v>176029.69319653</v>
+        <v>176029.6931965301</v>
       </c>
       <c r="G94" s="87" t="n">
         <v>194985.542673434</v>
@@ -9789,7 +9789,7 @@
         <v>139011.8572200891</v>
       </c>
       <c r="N94" s="86" t="n">
-        <v>151642.0994643109</v>
+        <v>151642.099464311</v>
       </c>
       <c r="O94" s="86" t="n">
         <v>163809.305024764</v>
@@ -9997,7 +9997,7 @@
         <v>164632.5371995057</v>
       </c>
       <c r="F96" s="133" t="n">
-        <v>177804.9021129451</v>
+        <v>177804.9021129452</v>
       </c>
       <c r="G96" s="134" t="n">
         <v>196971.3031150725</v>
@@ -10027,10 +10027,10 @@
         <v>165381.9337389295</v>
       </c>
       <c r="P96" s="133" t="n">
-        <v>178257.9360315528</v>
+        <v>178257.9360315529</v>
       </c>
       <c r="Q96" s="134" t="n">
-        <v>197081.6897489414</v>
+        <v>197081.6897489415</v>
       </c>
       <c r="S96" s="51" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>134134.6560107474</v>
       </c>
       <c r="U96" s="136" t="n">
-        <v>146623.3159113499</v>
+        <v>146623.31591135</v>
       </c>
       <c r="V96" s="136" t="n">
         <v>158659.1680496694</v>
@@ -10050,7 +10050,7 @@
         <v>171340.916914783</v>
       </c>
       <c r="X96" s="137" t="n">
-        <v>189771.324196888</v>
+        <v>189771.3241968881</v>
       </c>
       <c r="Y96" s="135" t="n">
         <v>1084.42625463546</v>
@@ -10071,7 +10071,7 @@
         <v>135219.0822653829</v>
       </c>
       <c r="AE96" s="136" t="n">
-        <v>147491.367183386</v>
+        <v>147491.3671833861</v>
       </c>
       <c r="AF96" s="136" t="n">
         <v>159293.4308909304</v>
